--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-transport-du-patient.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-transport-du-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3029" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3029" uniqueCount="375">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -784,6 +784,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Act.statusCode</t>
@@ -6650,7 +6654,7 @@
         <v>74</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>74</v>
@@ -6658,10 +6662,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6717,25 +6721,25 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6755,10 +6759,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6781,13 +6785,13 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6838,7 +6842,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6858,10 +6862,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6959,10 +6963,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6985,11 +6989,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7040,7 +7044,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7060,10 +7064,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7090,12 +7094,12 @@
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
@@ -7121,7 +7125,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -7139,7 +7143,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7159,17 +7163,17 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>75</v>
@@ -7187,13 +7191,13 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7244,7 +7248,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7264,17 +7268,17 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>80</v>
@@ -7292,11 +7296,11 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7347,7 +7351,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7367,17 +7371,17 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>80</v>
@@ -7395,11 +7399,11 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7450,7 +7454,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7470,17 +7474,17 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>75</v>
@@ -7498,13 +7502,13 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7555,7 +7559,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7575,10 +7579,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7601,7 +7605,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7634,7 +7638,7 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -7652,7 +7656,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7672,10 +7676,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7731,25 +7735,25 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7769,10 +7773,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7795,7 +7799,7 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7848,7 +7852,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7868,10 +7872,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7894,7 +7898,7 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -7947,7 +7951,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7967,10 +7971,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7993,13 +7997,13 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8050,7 +8054,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8070,10 +8074,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8096,7 +8100,7 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -8149,7 +8153,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8169,10 +8173,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8195,7 +8199,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8248,7 +8252,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8268,10 +8272,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8294,13 +8298,13 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8351,7 +8355,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8371,10 +8375,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8397,13 +8401,13 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8454,7 +8458,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8474,10 +8478,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8575,10 +8579,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8676,10 +8680,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8777,10 +8781,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8878,10 +8882,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8981,10 +8985,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9084,10 +9088,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9187,10 +9191,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9290,10 +9294,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9391,10 +9395,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9431,7 +9435,7 @@
         <v>74</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>74</v>
@@ -9450,7 +9454,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -9468,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
@@ -9488,10 +9492,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9518,7 +9522,7 @@
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9569,7 +9573,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9589,10 +9593,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9619,12 +9623,12 @@
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
@@ -9670,7 +9674,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9690,10 +9694,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9769,7 +9773,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9789,10 +9793,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9815,7 +9819,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9868,7 +9872,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9888,10 +9892,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9914,7 +9918,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -9967,7 +9971,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9987,10 +9991,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10013,7 +10017,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -10066,7 +10070,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10086,10 +10090,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10112,7 +10116,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10165,7 +10169,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10185,10 +10189,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10211,7 +10215,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10264,7 +10268,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10284,10 +10288,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10310,7 +10314,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10363,7 +10367,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10383,10 +10387,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10409,7 +10413,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10462,7 +10466,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10482,10 +10486,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10508,7 +10512,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10561,7 +10565,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10581,10 +10585,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10607,7 +10611,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10660,7 +10664,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10680,10 +10684,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10706,7 +10710,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10759,7 +10763,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10779,10 +10783,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10805,7 +10809,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10858,7 +10862,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10878,10 +10882,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10904,7 +10908,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10957,7 +10961,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10977,10 +10981,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11003,7 +11007,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11056,7 +11060,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11076,10 +11080,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11102,7 +11106,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11155,7 +11159,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11175,10 +11179,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11201,7 +11205,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11254,7 +11258,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
